--- a/data.xlsx
+++ b/data.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yana.k\.cursor\projects\empty-window\nps-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52503D2-9878-47B0-833E-9A164FFD7DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D068CD-7739-426D-A774-461D345C4985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{74487427-0345-4DD6-8246-25E85D8ABC71}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$1001</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1258,7 +1261,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="[$-419]mmmm;@"/>
+    <numFmt numFmtId="164" formatCode="[$-419]mmmm;@"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1558,16 +1561,16 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -17216,8 +17219,8 @@
       <c r="D831" s="4">
         <v>10</v>
       </c>
-      <c r="E831" s="13" t="s">
-        <v>7</v>
+      <c r="E831" s="14" t="s">
+        <v>12</v>
       </c>
       <c r="F831" s="49">
         <v>46143</v>
@@ -20350,6 +20353,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F1001" xr:uid="{00E7C04E-E951-46F4-8B3C-4B7BD4F110CB}"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" sqref="D2:D78 D80:D1001" xr:uid="{C476BCF6-7B29-44D5-A4F2-9C68A224B066}">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10"</formula1>
